--- a/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3322" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3490" uniqueCount="883">
   <si>
     <t>Notes</t>
   </si>
@@ -2435,6 +2435,258 @@
   </si>
   <si>
     <t>Tue Jul 07 16:28:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 05:20:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 05:33:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 05:46:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 05:59:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 06:13:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 06:26:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 06:39:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 06:51:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 07:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 07:15:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 07:27:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 07:39:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 07:52:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 08:04:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 08:16:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 08:29:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 08:43:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 08:56:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 09:09:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 09:23:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 09:36:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 03:23:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 03:36:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 03:49:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 04:03:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 04:16:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 04:29:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 04:42:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 04:54:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 05:07:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 05:19:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 05:31:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 05:43:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 05:56:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 06:09:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 06:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 06:33:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 06:47:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 07:00:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 07:13:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 07:26:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 07:39:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 01:19:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 01:26:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 01:33:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 01:40:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 01:47:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 01:52:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 01:58:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:05:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:10:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:17:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:29:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:36:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:43:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:49:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 02:54:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 03:00:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 03:07:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 03:13:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 03:21:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 03:27:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:27:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:29:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:31:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:32:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:33:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:34:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:36:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:37:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:38:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:39:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:40:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:41:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:42:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:43:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:44:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:45:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:46:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:47:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:48:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:49:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:50:43 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2935,7 +3187,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>793</v>
+        <v>877</v>
       </c>
       <c r="C2" t="s" s="1">
         <v>74</v>
@@ -3016,7 +3268,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>794</v>
+        <v>878</v>
       </c>
       <c r="C3" t="s" s="1">
         <v>74</v>
@@ -3097,7 +3349,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>795</v>
+        <v>879</v>
       </c>
       <c r="C4" t="s" s="1">
         <v>74</v>
@@ -3178,7 +3430,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>796</v>
+        <v>880</v>
       </c>
       <c r="C5" t="s" s="1">
         <v>74</v>
@@ -3259,7 +3511,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>797</v>
+        <v>881</v>
       </c>
       <c r="C6" t="s" s="1">
         <v>74</v>
@@ -3340,7 +3592,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>798</v>
+        <v>882</v>
       </c>
       <c r="C7" t="s" s="1">
         <v>74</v>
@@ -3554,7 +3806,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>778</v>
+        <v>862</v>
       </c>
       <c r="C2" t="s" s="1">
         <v>74</v>
@@ -3635,7 +3887,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>779</v>
+        <v>863</v>
       </c>
       <c r="C3" t="s" s="1">
         <v>74</v>
@@ -3716,7 +3968,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>780</v>
+        <v>864</v>
       </c>
       <c r="C4" t="s" s="1">
         <v>74</v>
@@ -3797,7 +4049,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>781</v>
+        <v>865</v>
       </c>
       <c r="C5" t="s" s="1">
         <v>74</v>
@@ -3878,7 +4130,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>782</v>
+        <v>866</v>
       </c>
       <c r="C6" t="s" s="1">
         <v>74</v>
@@ -3959,7 +4211,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>783</v>
+        <v>867</v>
       </c>
       <c r="C7" t="s" s="1">
         <v>74</v>
@@ -4175,7 +4427,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>784</v>
+        <v>868</v>
       </c>
       <c r="C2" t="s" s="1">
         <v>74</v>
@@ -4250,7 +4502,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>785</v>
+        <v>869</v>
       </c>
       <c r="C3" t="s" s="1">
         <v>74</v>
@@ -4325,7 +4577,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>786</v>
+        <v>870</v>
       </c>
       <c r="C4" t="s" s="1">
         <v>74</v>
@@ -4400,10 +4652,10 @@
     </row>
     <row ht="43.2" r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="1">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>787</v>
+        <v>871</v>
       </c>
       <c r="C5" t="s" s="1">
         <v>74</v>
@@ -4478,7 +4730,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>788</v>
+        <v>872</v>
       </c>
       <c r="C6" t="s" s="1">
         <v>74</v>
@@ -4553,7 +4805,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>789</v>
+        <v>873</v>
       </c>
       <c r="C7" t="s" s="1">
         <v>74</v>
@@ -4631,7 +4883,7 @@
         <v>74</v>
       </c>
       <c r="B8" t="s" s="1">
-        <v>790</v>
+        <v>874</v>
       </c>
       <c r="C8" t="s" s="1">
         <v>74</v>
@@ -4706,7 +4958,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s" s="1">
-        <v>791</v>
+        <v>875</v>
       </c>
       <c r="C9" t="s" s="1">
         <v>74</v>
@@ -4781,7 +5033,7 @@
         <v>74</v>
       </c>
       <c r="B10" t="s" s="1">
-        <v>792</v>
+        <v>876</v>
       </c>
       <c r="C10" t="s" s="1">
         <v>74</v>

--- a/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3490" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3494" uniqueCount="885">
   <si>
     <t>Notes</t>
   </si>
@@ -2687,6 +2687,12 @@
   </si>
   <si>
     <t>Fri Oct 23 06:50:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 20:47:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 20:55:54 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3806,7 +3812,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="C2" t="s" s="1">
         <v>74</v>
@@ -3887,7 +3893,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="C3" t="s" s="1">
         <v>74</v>
